--- a/data/trans_orig/IP19C05-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP19C05-Provincia-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3170</t>
+          <t>3490</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3066</t>
+          <t>3203</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16151</t>
+          <t>15831</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42773</t>
+          <t>42636</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>3148</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5633</t>
+          <t>5115</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>635</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6373</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>54013</t>
+          <t>54074</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>59342</t>
+          <t>59860</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>115824</t>
+          <t>116050</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>121566</t>
+          <t>121562</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4155</t>
+          <t>5144</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4260</t>
+          <t>5075</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37804</t>
+          <t>36815</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>79340</t>
+          <t>78525</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2837</t>
+          <t>3012</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>3118</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23354</t>
+          <t>23179</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>45638</t>
+          <t>45541</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3895</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3502</t>
+          <t>3273</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>64134</t>
+          <t>64178</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>129812</t>
+          <t>130041</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3587</t>
+          <t>3447</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4565</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>5378</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>77733</t>
+          <t>77873</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>69848</t>
+          <t>70157</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>150223</t>
+          <t>150356</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>155095</t>
+          <t>155734</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1237</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7840</t>
+          <t>7453</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,47 +3491,47 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>1299</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>8508</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
           <t>0,36%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>3532</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>1317</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>7925</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>3505</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>12639</t>
+          <t>12640</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>343090</t>
+          <t>343477</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>349664</t>
+          <t>349693</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,49 +3604,49 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
+          <t>99,65%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>358199</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>353223</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>360432</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>99,02%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>97,65%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
           <t>99,64%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>540</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>358199</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>353806</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>360414</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,02%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>97,81%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>99,64%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>1057</t>
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>700022</t>
+          <t>700021</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>708970</t>
+          <t>709156</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3802</t>
+          <t>3947</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3945</t>
+          <t>3705</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25857</t>
+          <t>25712</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48089</t>
+          <t>48329</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>952</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7522</t>
+          <t>7644</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3974</t>
+          <t>4595</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9749</t>
+          <t>9516</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45522</t>
+          <t>45400</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>52121</t>
+          <t>52092</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53658</t>
+          <t>53037</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>100928</t>
+          <t>101161</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>108740</t>
+          <t>109052</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3435</t>
+          <t>2646</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3281</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36010</t>
+          <t>36799</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>69627</t>
+          <t>69145</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2312</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4365</t>
+          <t>4718</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>439</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4882</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39486</t>
+          <t>39045</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36861</t>
+          <t>36508</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>78142</t>
+          <t>78086</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>82581</t>
+          <t>82585</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>678</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5780</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4493</t>
+          <t>4530</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1428</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7955</t>
+          <t>7597</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,15%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20751</t>
+          <t>20288</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25391</t>
+          <t>25390</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23137</t>
+          <t>23100</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>45743</t>
+          <t>46101</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>52294</t>
+          <t>52270</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -5775,7 +5775,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3355</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3022</t>
+          <t>3379</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32071</t>
+          <t>30598</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>65563</t>
+          <t>65206</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3454</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3179</t>
+          <t>3207</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>60515</t>
+          <t>60676</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>127954</t>
+          <t>127926</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>609</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5350</t>
+          <t>6052</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3378</t>
+          <t>2843</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>765</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6448</t>
+          <t>6359</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>72497</t>
+          <t>71795</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>77241</t>
+          <t>77238</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>66709</t>
+          <t>67244</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>141486</t>
+          <t>141575</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>147303</t>
+          <t>147169</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>15210</t>
+          <t>15848</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2840</t>
+          <t>2848</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>11182</t>
+          <t>11619</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>9897</t>
+          <t>9716</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>23270</t>
+          <t>22836</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>338781</t>
+          <t>338143</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>348967</t>
+          <t>348732</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>354820</t>
+          <t>354383</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>363162</t>
+          <t>363154</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>696723</t>
+          <t>697157</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>710096</t>
+          <t>710277</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -7383,7 +7383,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4075</t>
+          <t>4261</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2559</t>
+          <t>2576</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7453,7 +7453,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5252</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -7491,7 +7491,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24491</t>
+          <t>24305</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27352</t>
+          <t>27335</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53292</t>
+          <t>53224</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t>4172</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7761,7 +7761,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3998</t>
+          <t>4397</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>658</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5526</t>
+          <t>5589</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>49296</t>
+          <t>49336</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>52735</t>
+          <t>52336</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>104715</t>
+          <t>104652</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>109584</t>
+          <t>109583</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -8407,12 +8407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>563</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4965</t>
+          <t>4821</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>557</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4905</t>
+          <t>5459</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8497,7 +8497,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -8520,12 +8520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>41580</t>
+          <t>41724</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>45981</t>
+          <t>45982</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>92643</t>
+          <t>92089</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>96992</t>
+          <t>96991</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>2834</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8785,12 +8785,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>846</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6017</t>
+          <t>6341</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8800,12 +8800,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8820,12 +8820,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>849</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7123</t>
+          <t>7645</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>23,81%</t>
         </is>
       </c>
     </row>
@@ -8863,7 +8863,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11741</t>
+          <t>12210</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8878,7 +8878,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8898,12 +8898,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11051</t>
+          <t>10727</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16227</t>
+          <t>16222</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8913,12 +8913,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8933,12 +8933,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24988</t>
+          <t>24466</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31247</t>
+          <t>31262</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,36%</t>
         </is>
       </c>
     </row>
@@ -9098,7 +9098,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3687</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4051</t>
+          <t>3678</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>36056</t>
+          <t>36725</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>76262</t>
+          <t>76635</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -9441,7 +9441,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5828</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3849</t>
+          <t>4016</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>655</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6623</t>
+          <t>7183</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -9549,7 +9549,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>61615</t>
+          <t>60902</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -9584,7 +9584,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>58094</t>
+          <t>57927</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>122763</t>
+          <t>122203</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>128733</t>
+          <t>128731</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>
@@ -9779,12 +9779,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>617</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5173</t>
+          <t>5348</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9794,12 +9794,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9819,7 +9819,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4567</t>
+          <t>5155</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7611</t>
+          <t>7683</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -9892,12 +9892,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>74079</t>
+          <t>73904</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>78639</t>
+          <t>78635</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9907,12 +9907,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>74091</t>
+          <t>73503</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>150299</t>
+          <t>150227</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>156602</t>
+          <t>156635</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>5262</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>15038</t>
+          <t>16245</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2928</t>
+          <t>2859</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>11394</t>
+          <t>11704</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10172,12 +10172,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>10024</t>
+          <t>9037</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>23039</t>
+          <t>23031</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,7 +10207,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>347580</t>
+          <t>346373</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>357703</t>
+          <t>357356</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>356614</t>
+          <t>356304</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>365080</t>
+          <t>365149</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>707587</t>
+          <t>707595</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>720602</t>
+          <t>721589</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
